--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_model[生物模型信息].xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureModel" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>id</t>
   </si>
@@ -109,7 +109,10 @@
     <t>Assets/LoadResources/Spine/Creature/Human/Human_SkeletonData.asset</t>
   </si>
   <si>
-    <t>2.5;0,-150</t>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>2.5;0,-120</t>
   </si>
   <si>
     <t>4;0,-150</t>
@@ -124,7 +127,7 @@
     <t>Assets/LoadResources/Spine/Creature/Skeleton/Skeleton_SkeletonData.asset</t>
   </si>
   <si>
-    <t>2.5;-10,-150</t>
+    <t>2.5;-10,-130</t>
   </si>
   <si>
     <t>4;-10,-150</t>
@@ -154,7 +157,7 @@
     <t>Assets/LoadResources/Spine/Creature/Succubus/Succubus_SkeletonData.asset</t>
   </si>
   <si>
-    <t>2.5;0,-130</t>
+    <t>2.5;0,-160</t>
   </si>
   <si>
     <t>4;0,-200</t>
@@ -169,10 +172,7 @@
     <t>Assets/LoadResources/Spine/Creature/Minotaur/Minotaur_SkeletonData.asset</t>
   </si>
   <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>1.8;-25,-100</t>
+    <t>1.8;-25,-80</t>
   </si>
   <si>
     <t>3.5;-20,-130</t>
@@ -187,7 +187,7 @@
     <t>Assets/LoadResources/Spine/Creature/Goblin/Goblin_SkeletonData.asset</t>
   </si>
   <si>
-    <t>3.5;-5,-110</t>
+    <t>3.5;-5,-100</t>
   </si>
   <si>
     <t>5;0,-100</t>
@@ -202,7 +202,7 @@
     <t>Assets/LoadResources/Spine/Creature/Orc/Orc_SkeletonData.asset</t>
   </si>
   <si>
-    <t>2.5;0,-180</t>
+    <t>2.5;0,-170</t>
   </si>
   <si>
     <t>3.5;10,-160</t>
@@ -226,21 +226,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Consolas"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,14 +245,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -263,7 +258,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,7 +265,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,7 +272,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -287,7 +279,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -295,14 +286,12 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,7 +299,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,7 +306,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -326,14 +313,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,35 +326,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -823,11 +803,161 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="52">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1178,318 +1308,318 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="46.625" customWidth="1"/>
-    <col min="3" max="3" width="84.125" customWidth="1"/>
-    <col min="4" max="4" width="29.375" customWidth="1"/>
-    <col min="5" max="5" width="22.375" customWidth="1"/>
-    <col min="6" max="6" width="103" customWidth="1"/>
-    <col min="7" max="7" width="62.625" customWidth="1"/>
-    <col min="8" max="8" width="17.375" customWidth="1"/>
-    <col min="9" max="9" width="62.625" customWidth="1"/>
-    <col min="10" max="10" width="42.875" customWidth="1"/>
-    <col min="11" max="11" width="25.125" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1" style="50"/>
+    <col min="2" max="2" width="46.625" customWidth="1" style="50"/>
+    <col min="3" max="3" width="84.125" customWidth="1" style="50"/>
+    <col min="4" max="4" width="29.375" customWidth="1" style="50"/>
+    <col min="5" max="5" width="22.375" customWidth="1" style="50"/>
+    <col min="6" max="6" width="14.875" customWidth="1" style="50"/>
+    <col min="7" max="7" width="62.625" customWidth="1" style="50"/>
+    <col min="8" max="8" width="17.375" customWidth="1" style="50"/>
+    <col min="9" max="9" width="62.625" customWidth="1" style="50"/>
+    <col min="10" max="10" width="42.875" customWidth="1" style="50"/>
+    <col min="11" max="11" width="25.125" customWidth="1" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="50" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="50" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="50" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:10">
-      <c r="A4">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="50">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="51">
         <v>300100301</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="50">
+        <v>1</v>
+      </c>
+      <c r="J4" s="50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="50">
+        <v>2</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="51">
+        <v>300200301</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="50">
+        <v>2</v>
+      </c>
+      <c r="J5" s="50" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="50">
+        <v>3</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="51">
+        <v>300300301</v>
+      </c>
+      <c r="E6" s="50">
         <v>1.3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G6" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="50">
+        <v>3</v>
+      </c>
+      <c r="J6" s="50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="50">
+        <v>4</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="51">
+        <v>300400301</v>
+      </c>
+      <c r="E7" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
+      <c r="G7" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="50">
+        <v>4</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:10">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="1">
-        <v>300200301</v>
-      </c>
-      <c r="E5">
-        <v>1.3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="50">
+        <v>5</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="51">
+        <v>300500301</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="50">
+        <v>5</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:10">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="1">
-        <v>300300301</v>
-      </c>
-      <c r="E6">
-        <v>1.3</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="50">
+        <v>6</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="51">
+        <v>300600301</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="50">
+        <v>6</v>
+      </c>
+      <c r="J9" s="50" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:10">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="1">
-        <v>300400301</v>
-      </c>
-      <c r="E7">
-        <v>1.3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:10">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="1">
-        <v>300500301</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" spans="1:10">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="1">
-        <v>300600301</v>
-      </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9">
-        <v>6</v>
-      </c>
-      <c r="J9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="1:10">
-      <c r="A10">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="50">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="51">
         <v>300700301</v>
       </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="E10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="50">
         <v>7</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="50" t="s">
         <v>58</v>
       </c>
     </row>
